--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B74C43-6A55-4BDA-8FC1-1DBFB90EE875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A488A9B2-4542-4D63-B100-D8011444304D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
     <sheet name="Constants" sheetId="2" r:id="rId2"/>
     <sheet name="Assets" sheetId="3" r:id="rId3"/>
-    <sheet name="InvoicePostProcessing" sheetId="4" r:id="rId4"/>
+    <sheet name="InvoicePostProcessing" sheetId="8" r:id="rId4"/>
     <sheet name="ReceiptPostProcessing" sheetId="5" r:id="rId5"/>
     <sheet name="AutocorrectOcrMistakes" sheetId="7" r:id="rId6"/>
   </sheets>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="250">
   <si>
     <t>Name</t>
   </si>
@@ -158,9 +158,6 @@
     <t>OrchestratorAssetFolderPath</t>
   </si>
   <si>
-    <t>DocumentUnderstandingApiKey</t>
-  </si>
-  <si>
     <t>ApiKey</t>
   </si>
   <si>
@@ -407,69 +404,33 @@
     <t>https://du.uipath.com/ie/invoices</t>
   </si>
   <si>
-    <t>LogMessage_InvoicePostProcessing</t>
-  </si>
-  <si>
-    <t>Starting Invoice Post Processing</t>
-  </si>
-  <si>
-    <t>LogMessage_InvoicePostProcessing_DateFailure</t>
-  </si>
-  <si>
     <t>Parsing the Date has failed!</t>
   </si>
   <si>
-    <t>LogMessage_InvoicePostProcessing_MandatoryFieldsFailure</t>
-  </si>
-  <si>
     <t>One or more of the mandatory were missing!</t>
   </si>
   <si>
-    <t>LogMessage_InvoicePostProcessing_LineAmountFailureMath</t>
-  </si>
-  <si>
     <t>Quantity * Unit-price is not equal to Line Amount!</t>
   </si>
   <si>
-    <t>LogMessage_InvoicePostProcessing_LineAmountFailureEmpty</t>
-  </si>
-  <si>
     <t>Quantity or Unit-price is Empty!</t>
   </si>
   <si>
-    <t>LogMessage_InvoicePostProcessing_AlreadySetFalse</t>
-  </si>
-  <si>
     <t>AutoExtraction is already set to false in a previous step. Skipping rest of checks.</t>
   </si>
   <si>
-    <t>LogMessage_InvoicePostProcessing_SubtotalFailure</t>
-  </si>
-  <si>
     <t>Subtotal Failure with subtotal: {0} and net-amount {1}</t>
   </si>
   <si>
-    <t>LogMessage_InvoicePostProcessing_TotalFailure</t>
-  </si>
-  <si>
     <t>Total Computation Failed!</t>
   </si>
   <si>
-    <t>LogMessage_InvoicePostProcessing_SubtotalPass</t>
-  </si>
-  <si>
     <t>Subtotal Pass with subtotal: {0} and net-amount {1}</t>
   </si>
   <si>
-    <t>LogMessage_InvoicePostProcessing_ConfidenceFieldsFailure</t>
-  </si>
-  <si>
     <t xml:space="preserve">These are the fields that failed: </t>
   </si>
   <si>
-    <t>SubTotalAdditions</t>
-  </si>
-  <si>
     <t>Each field present in the list here, will be added to the subtotal to compute the total</t>
   </si>
   <si>
@@ -479,9 +440,6 @@
     <t>These fields are mandatory. If they have not been extracted at all, the document will be sent for validation</t>
   </si>
   <si>
-    <t>MandatoryColumnFields</t>
-  </si>
-  <si>
     <t>These column fields are mandatory. If they have not been extracted at all, the document will be sent for validation</t>
   </si>
   <si>
@@ -500,364 +458,334 @@
     <t>other-Confidence</t>
   </si>
   <si>
-    <t>Date,Invoice Number,PO Number,Total</t>
-  </si>
-  <si>
-    <t>Tax Amount,Shipping Charges,Discount</t>
-  </si>
-  <si>
-    <t>Date,Shipping Address,Invoice Number,PO Number</t>
-  </si>
-  <si>
-    <t>Quantity,Unit Price,Line Amount</t>
-  </si>
-  <si>
-    <t>Date-Confidence</t>
-  </si>
-  <si>
-    <t>Shipping Address-Confidence</t>
-  </si>
-  <si>
-    <t>Invoice Number-Confidence</t>
-  </si>
-  <si>
-    <t>PO Number-Confidence</t>
+    <t>AlwaysValidateClassification</t>
+  </si>
+  <si>
+    <t>LogMessage_ExtractionBusinessRuleValidationStart</t>
+  </si>
+  <si>
+    <t>Extraction Business Rule Validation started for:</t>
+  </si>
+  <si>
+    <t>LogMessage_ClassificationBusinessRuleValidationStart</t>
+  </si>
+  <si>
+    <t>Classification Business Rule Validation started for:</t>
+  </si>
+  <si>
+    <t>AlwaysValidateExtraction</t>
+  </si>
+  <si>
+    <t>Creating classification validation action</t>
+  </si>
+  <si>
+    <t>Waiting on data validation action #</t>
+  </si>
+  <si>
+    <t>Waiting on classification validation action #</t>
+  </si>
+  <si>
+    <t>Data extraction finished</t>
+  </si>
+  <si>
+    <t>Classification finished</t>
+  </si>
+  <si>
+    <t>Process was aborted due to {0} with message: {1} Full Exception: {2}</t>
+  </si>
+  <si>
+    <t>Failed to process page range {0} in file {1} due to {2} with message: {3} Full Exception: {4}</t>
+  </si>
+  <si>
+    <t>SkipClassifierTraining</t>
+  </si>
+  <si>
+    <t>SkipExtractorTraining</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>If set to True, classification will always go through manual validation. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>If set to True, extracted data will always go through manual validation. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>If set to True, classifier training will not be performed. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>If set to True, extractor training will not be performed. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>Validating Extracted Data</t>
+  </si>
+  <si>
+    <t>Auxiliary folder where the job will download files when resuming after a human-in-the-loop action. Only used if downloading the files is enabled</t>
+  </si>
+  <si>
+    <t>Resuming after data validation{0}. Document: {1}</t>
+  </si>
+  <si>
+    <t>Resuming after classification validation{0}. Document(s) classified as: {1}</t>
+  </si>
+  <si>
+    <t>Action Catalog Name. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>Path to the Orchestrator Folder where the Action Catalog resides. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>Storage Bucket Name (required when Action Center is used). Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>Path inside  the Storage Bucket where actions will store the files. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>The name of the Orchestrator Queue. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>Path to the Orchestrator Folder where the Queue resides. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>ClassificationThreshold</t>
+  </si>
+  <si>
+    <t>Classification threshold for Classification Business Rule Validation must be a value between 0 and 1.</t>
+  </si>
+  <si>
+    <t>LogMessage_ReceiptPostProcessing</t>
+  </si>
+  <si>
+    <t>Starting Receipt Post Processing</t>
+  </si>
+  <si>
+    <t>LogMessage_ReceiptPostProcessing_DateFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_ReceiptPostProcessing_MandatoryFieldsFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_ReceiptPostProcessing_AlreadySetFalse</t>
+  </si>
+  <si>
+    <t>LogMessage_ReceiptPostProcessing_TotalFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_ReceiptPostProcessing_SubtotalPass</t>
+  </si>
+  <si>
+    <t>Subtotal Pass with subtotal: {0}</t>
+  </si>
+  <si>
+    <t>LogMessage_ReceiptPostProcessing_ConfidenceFieldsFailure</t>
+  </si>
+  <si>
+    <t>SubTotalAdditionsReceipt</t>
+  </si>
+  <si>
+    <t>Tax Amount</t>
+  </si>
+  <si>
+    <t>MandatoryFieldsReceipt</t>
+  </si>
+  <si>
+    <t>Receipt Number,Tax Amount,Total Value,Receipt Date</t>
+  </si>
+  <si>
+    <t>MandatoryColumnFieldsReceipt</t>
+  </si>
+  <si>
+    <t>Line Amount</t>
+  </si>
+  <si>
+    <t>ConfidenceFieldsReceipt</t>
+  </si>
+  <si>
+    <t>Receipt Date,Receipt Number</t>
+  </si>
+  <si>
+    <t>OtherConfidenceFieldsReceipt</t>
+  </si>
+  <si>
+    <t>Phone Number,Tax Amount,Total Value</t>
+  </si>
+  <si>
+    <t>Receipt Date-Confidence</t>
+  </si>
+  <si>
+    <t>Receipt Number-Confidence</t>
+  </si>
+  <si>
+    <t>otherReceipt-Confidence</t>
+  </si>
+  <si>
+    <t>LogMessage_TransactionItemNotFound</t>
+  </si>
+  <si>
+    <t>No transaction item found in the queue</t>
+  </si>
+  <si>
+    <t>LogMessage_TargetFileMissingInTransactionItem</t>
+  </si>
+  <si>
+    <t>Transaction Item does not specify the file to be processed</t>
+  </si>
+  <si>
+    <t>TargetFileKey</t>
+  </si>
+  <si>
+    <t>Key in the Transaction Item's dictionary that holds the path to the file to be processed</t>
+  </si>
+  <si>
+    <t>LogMessage_SetTransactionProgress</t>
+  </si>
+  <si>
+    <t>Updating transaction progress to:</t>
+  </si>
+  <si>
+    <t>https://du.uipath.com/svc/formextractor</t>
+  </si>
+  <si>
+    <t>FormExtractorEndpoint</t>
+  </si>
+  <si>
+    <t>UiPath public endpoint for Form Extractor</t>
+  </si>
+  <si>
+    <t>AutocorrectStorageBucketDirectoryPath</t>
+  </si>
+  <si>
+    <t>Path inside the Storage Bucket where the autocorrect file is stored. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>MinimumNumberOfRepetitions</t>
+  </si>
+  <si>
+    <t>The minimum number of times the value needs to be corrected in Action Center before the flow will start to autocorrect. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>AutocorrectionEnabled</t>
+  </si>
+  <si>
+    <t>A flag that determines if autocorrection should be called or not. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>LogMessage_AutocorrectOcrMistakesStart</t>
+  </si>
+  <si>
+    <t>OCR Autocorrection started</t>
+  </si>
+  <si>
+    <t>LogMessage_AutocorrectOcrMistakesFinished</t>
+  </si>
+  <si>
+    <t>OCR Autocorrection finished</t>
+  </si>
+  <si>
+    <t>MaxExecutionAttemptsHigh</t>
+  </si>
+  <si>
+    <t>Maximum number of execution attempts for a process step which by default is high.</t>
+  </si>
+  <si>
+    <t>RetryIntervalLow</t>
+  </si>
+  <si>
+    <t>AutocorrectionLearningFile.json</t>
+  </si>
+  <si>
+    <t>AutocorrectionFieldIdList</t>
+  </si>
+  <si>
+    <t>A comma separated list of the taxonomy ids of the fields we want to enable autocorrection for. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>DU_DateFormats</t>
+  </si>
+  <si>
+    <t>Different date formats.</t>
+  </si>
+  <si>
+    <t>yyyy-MM-dd;dd-MM-yyyy;MM-dd-yyyy;MM/dd/yyyy;dd/MM/yyyy;yyyy/MM/dd;dd.MM.yyyy;MM.dd.yyyy;yyyy.MM.dd</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>API_Key</t>
+  </si>
+  <si>
+    <t>chaitanya.ravindra@accelirate.com's workspace</t>
+  </si>
+  <si>
+    <t>DU_ConocoPhillips</t>
+  </si>
+  <si>
+    <t>ConocoPhillipsStatements</t>
+  </si>
+  <si>
+    <t>SettlementStatements</t>
   </si>
   <si>
     <t>True</t>
   </si>
   <si>
-    <t>AlwaysValidateClassification</t>
-  </si>
-  <si>
-    <t>LogMessage_ExtractionBusinessRuleValidationStart</t>
-  </si>
-  <si>
-    <t>Extraction Business Rule Validation started for:</t>
-  </si>
-  <si>
-    <t>LogMessage_ClassificationBusinessRuleValidationStart</t>
-  </si>
-  <si>
-    <t>Classification Business Rule Validation started for:</t>
-  </si>
-  <si>
-    <t>AlwaysValidateExtraction</t>
-  </si>
-  <si>
-    <t>Creating classification validation action</t>
-  </si>
-  <si>
-    <t>Waiting on data validation action #</t>
-  </si>
-  <si>
-    <t>Waiting on classification validation action #</t>
-  </si>
-  <si>
-    <t>Data extraction finished</t>
-  </si>
-  <si>
-    <t>Classification finished</t>
-  </si>
-  <si>
-    <t>Process was aborted due to {0} with message: {1} Full Exception: {2}</t>
-  </si>
-  <si>
-    <t>Failed to process page range {0} in file {1} due to {2} with message: {3} Full Exception: {4}</t>
-  </si>
-  <si>
-    <t>SkipClassifierTraining</t>
-  </si>
-  <si>
-    <t>SkipExtractorTraining</t>
-  </si>
-  <si>
-    <t>False</t>
-  </si>
-  <si>
-    <t>If set to True, classification will always go through manual validation. Asset value overwrites the one from the "Settings" sheet</t>
-  </si>
-  <si>
-    <t>If set to True, extracted data will always go through manual validation. Asset value overwrites the one from the "Settings" sheet</t>
-  </si>
-  <si>
-    <t>If set to True, classification will always go through manual validation. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>If set to True, extracted data will always go through manual validation. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>If set to True, classifier training will not be performed. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>If set to True, extractor training will not be performed. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>If set to True, classifier training will not be performed. Asset value overwrites the one from the "Settings" sheet</t>
-  </si>
-  <si>
-    <t>If set to True, extractor training will not be performed. Asset value overwrites the one from the "Settings" sheet</t>
-  </si>
-  <si>
-    <t>Validating Extracted Data</t>
-  </si>
-  <si>
-    <t>Auxiliary folder where the job will download files when resuming after a human-in-the-loop action. Only used if downloading the files is enabled</t>
-  </si>
-  <si>
-    <t>Resuming after data validation{0}. Document: {1}</t>
-  </si>
-  <si>
-    <t>Resuming after classification validation{0}. Document(s) classified as: {1}</t>
-  </si>
-  <si>
-    <t>DU_StorageBucketName</t>
-  </si>
-  <si>
-    <t>DU_StorageBucketDirectoryPath</t>
-  </si>
-  <si>
-    <t>DU_ActionFolderPath</t>
-  </si>
-  <si>
-    <t>DU_ActionCatalogName</t>
-  </si>
-  <si>
-    <t>DU_QueueName</t>
-  </si>
-  <si>
-    <t>DU_QueuePath</t>
-  </si>
-  <si>
-    <t>Action Catalog Name. The asset value overrides the one from the "Settings" sheet</t>
-  </si>
-  <si>
-    <t>Path to the Orchestrator Folder where the Action Catalog resides. The asset value overrides the one from the "Settings" sheet</t>
-  </si>
-  <si>
-    <t>Storage Bucket Name (required when Action Center is used). The asset value overrides the one from the "Settings" sheet</t>
-  </si>
-  <si>
-    <t>Path inside  the Storage Bucket where actions will store the files. The asset value overrides the one from the "Settings" sheet</t>
-  </si>
-  <si>
-    <t>The name of the Orchestrator Queue. The asset value overrides the one from the "Settings" sheet</t>
-  </si>
-  <si>
-    <t>Path to the Orchestrator Folder where the Queue resides. The asset value overrides the one from the "Settings" sheet</t>
-  </si>
-  <si>
-    <t>Action Catalog Name. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>Path to the Orchestrator Folder where the Action Catalog resides. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>Storage Bucket Name (required when Action Center is used). Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>Path inside  the Storage Bucket where actions will store the files. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>The name of the Orchestrator Queue. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>Path to the Orchestrator Folder where the Queue resides. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>ClassificationThreshold</t>
-  </si>
-  <si>
-    <t>Classification threshold for Classification Business Rule Validation must be a value between 0 and 1.</t>
-  </si>
-  <si>
-    <t>DU_ClassificationThreshold</t>
-  </si>
-  <si>
-    <t>LogMessage_ReceiptPostProcessing</t>
-  </si>
-  <si>
-    <t>Starting Receipt Post Processing</t>
-  </si>
-  <si>
-    <t>LogMessage_ReceiptPostProcessing_DateFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_ReceiptPostProcessing_MandatoryFieldsFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_ReceiptPostProcessing_AlreadySetFalse</t>
-  </si>
-  <si>
-    <t>LogMessage_ReceiptPostProcessing_TotalFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_ReceiptPostProcessing_SubtotalPass</t>
-  </si>
-  <si>
-    <t>Subtotal Pass with subtotal: {0}</t>
-  </si>
-  <si>
-    <t>LogMessage_ReceiptPostProcessing_ConfidenceFieldsFailure</t>
-  </si>
-  <si>
-    <t>SubTotalAdditionsReceipt</t>
-  </si>
-  <si>
-    <t>Tax Amount</t>
-  </si>
-  <si>
-    <t>MandatoryFieldsReceipt</t>
-  </si>
-  <si>
-    <t>Receipt Number,Tax Amount,Total Value,Receipt Date</t>
-  </si>
-  <si>
-    <t>MandatoryColumnFieldsReceipt</t>
-  </si>
-  <si>
-    <t>Line Amount</t>
-  </si>
-  <si>
-    <t>ConfidenceFieldsReceipt</t>
-  </si>
-  <si>
-    <t>Receipt Date,Receipt Number</t>
-  </si>
-  <si>
-    <t>OtherConfidenceFieldsReceipt</t>
-  </si>
-  <si>
-    <t>Phone Number,Tax Amount,Total Value</t>
-  </si>
-  <si>
-    <t>Receipt Date-Confidence</t>
-  </si>
-  <si>
-    <t>Receipt Number-Confidence</t>
-  </si>
-  <si>
-    <t>otherReceipt-Confidence</t>
-  </si>
-  <si>
-    <t>LogMessage_TransactionItemNotFound</t>
-  </si>
-  <si>
-    <t>No transaction item found in the queue</t>
-  </si>
-  <si>
-    <t>LogMessage_TargetFileMissingInTransactionItem</t>
-  </si>
-  <si>
-    <t>Transaction Item does not specify the file to be processed</t>
-  </si>
-  <si>
-    <t>TargetFileKey</t>
-  </si>
-  <si>
-    <t>Key in the Transaction Item's dictionary that holds the path to the file to be processed</t>
-  </si>
-  <si>
-    <t>LogMessage_SetTransactionProgress</t>
-  </si>
-  <si>
-    <t>Updating transaction progress to:</t>
-  </si>
-  <si>
-    <t>https://du.uipath.com/svc/formextractor</t>
-  </si>
-  <si>
-    <t>FormExtractorEndpoint</t>
-  </si>
-  <si>
-    <t>DU_InputQueue</t>
-  </si>
-  <si>
-    <t>UiPath public endpoint for Form Extractor</t>
-  </si>
-  <si>
-    <t>AutocorrectStorageBucketDirectoryPath</t>
-  </si>
-  <si>
-    <t>Path inside the Storage Bucket where the autocorrect file is stored. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>MinimumNumberOfRepetitions</t>
-  </si>
-  <si>
-    <t>The minimum number of times the value needs to be corrected in Action Center before the flow will start to autocorrect. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>AutocorrectionEnabled</t>
-  </si>
-  <si>
-    <t>A flag that determines if autocorrection should be called or not. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>DU_AutocorrectStorageBucketDirectoryPath</t>
-  </si>
-  <si>
-    <t>Path inside the Storage Bucket where the autocorrect file is stored. The asset value overrides the one from the "AutocorrectOcrMistakes" sheet</t>
-  </si>
-  <si>
-    <t>DU_MinimumNumberOfRepetitions</t>
-  </si>
-  <si>
-    <t>The minimum number of times the value needs to be corrected in Action Center before the flow will start to autocorrect. The asset value overrides the one from the "AutocorrectOcrMistakes" sheet</t>
-  </si>
-  <si>
-    <t>DU_AutocorrectionEnabled</t>
-  </si>
-  <si>
-    <t>A flag that determines if autocorrection should be called or not. The asset value overrides the one from the "AutocorrectOcrMistakes" sheet</t>
-  </si>
-  <si>
-    <t>LogMessage_AutocorrectOcrMistakesStart</t>
-  </si>
-  <si>
-    <t>OCR Autocorrection started</t>
-  </si>
-  <si>
-    <t>LogMessage_AutocorrectOcrMistakesFinished</t>
-  </si>
-  <si>
-    <t>OCR Autocorrection finished</t>
-  </si>
-  <si>
-    <t>MaxExecutionAttemptsHigh</t>
-  </si>
-  <si>
-    <t>Maximum number of execution attempts for a process step which by default is high.</t>
-  </si>
-  <si>
-    <t>RetryIntervalLow</t>
-  </si>
-  <si>
-    <t>AutocorrectionLearningFile.json</t>
-  </si>
-  <si>
-    <t>AutocorrectionFieldIdList</t>
-  </si>
-  <si>
-    <t>A comma separated list of the taxonomy ids of the fields we want to enable autocorrection for. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
-    <t>DU_AutocorrectionFieldIdList</t>
-  </si>
-  <si>
-    <t>DU_DateFormats</t>
-  </si>
-  <si>
-    <t>Different date formats.</t>
-  </si>
-  <si>
-    <t>yyyy-MM-dd;dd-MM-yyyy;MM-dd-yyyy;MM/dd/yyyy;dd/MM/yyyy;yyyy/MM/dd;dd.MM.yyyy;MM.dd.yyyy;yyyy.MM.dd</t>
-  </si>
-  <si>
-    <t>Tax Amount,Net Amount,Discount,Shipping Charges,Billing Name,Total, Name, Vendor Address, Billing Address, Billing VAT Number, Payment Address, Vendor VAT Number, DueDate,Payment Terms</t>
-  </si>
-  <si>
-    <t>Path</t>
+    <t>LogMessage_SettlementPostProcessing</t>
+  </si>
+  <si>
+    <t>Starting Settlement Post Processing</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_DateFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_MandatoryFieldsFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_LineAmountFailureMath</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_LineAmountFailureEmpty</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_AlreadySetFalse</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_SubtotalFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_TotalFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_SubtotalPass</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_ConfidenceFieldsFailure</t>
+  </si>
+  <si>
+    <t>Meter Number,Meter Name,Production Date,Pressure Base,MCF,MMBTU</t>
+  </si>
+  <si>
+    <t>BTU,Basis,Allocation Decimal,Gas Lift MCF,Gas Lift MMBTU1,Diverted Gas MCF,Diverted Gas MMBTU</t>
+  </si>
+  <si>
+    <t>Meter Number-Confidence</t>
+  </si>
+  <si>
+    <t>Meter Name-Confidence</t>
+  </si>
+  <si>
+    <t>Production Date-Confidence</t>
+  </si>
+  <si>
+    <t>Pressure Base-Confidence</t>
+  </si>
+  <si>
+    <t>MCF-Confidence</t>
+  </si>
+  <si>
+    <t>MMBTU-Confidence</t>
   </si>
 </sst>
 </file>
@@ -929,7 +857,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -940,6 +868,7 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1328,13 +1257,13 @@
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1342,7 +1271,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -1350,48 +1279,48 @@
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
         <v>50</v>
-      </c>
-      <c r="B8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
         <v>42</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1399,10 +1328,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1410,77 +1339,77 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
         <v>87</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="B14" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1490,13 +1419,13 @@
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="B21">
         <v>0.5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>210</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1504,13 +1433,13 @@
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="C23" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1518,13 +1447,13 @@
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="C25" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1534,53 +1463,66 @@
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="2"/>
+      <c r="B27" t="s">
+        <v>227</v>
+      </c>
       <c r="C27" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
+      <c r="B28" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="C28" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="2"/>
+      <c r="B29" t="s">
+        <v>228</v>
+      </c>
       <c r="C29" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>113</v>
+      </c>
+      <c r="B30" t="s">
+        <v>226</v>
       </c>
       <c r="C30" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="C31" t="s">
-        <v>207</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="B32" t="s">
+        <v>226</v>
       </c>
       <c r="C32" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2617,84 +2559,84 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>262</v>
+        <v>215</v>
       </c>
       <c r="B7">
         <v>99999</v>
       </c>
       <c r="C7" t="s">
-        <v>263</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B8">
         <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9">
         <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2736,15 +2678,15 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2757,15 +2699,15 @@
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
         <v>32</v>
@@ -2773,34 +2715,34 @@
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2813,18 +2755,18 @@
     </row>
     <row r="27" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" t="s">
         <v>91</v>
-      </c>
-      <c r="B27" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
         <v>53</v>
-      </c>
-      <c r="B28" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2832,47 +2774,47 @@
         <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2885,18 +2827,18 @@
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>260</v>
+        <v>213</v>
       </c>
       <c r="B37" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2904,7 +2846,7 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2917,143 +2859,143 @@
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" t="s">
         <v>119</v>
-      </c>
-      <c r="B44" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" t="s">
         <v>94</v>
-      </c>
-      <c r="B46" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" t="s">
         <v>112</v>
-      </c>
-      <c r="B50" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="B51" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="B52" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" t="s">
         <v>102</v>
-      </c>
-      <c r="B53" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" t="s">
         <v>106</v>
-      </c>
-      <c r="B54" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="B56" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" t="s">
         <v>99</v>
-      </c>
-      <c r="B58" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B59" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3078,7 +3020,7 @@
         <v>31</v>
       </c>
       <c r="B65" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4098,58 +4040,35 @@
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>225</v>
+      </c>
+      <c r="C2" t="s">
+        <v>226</v>
       </c>
       <c r="D2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>180</v>
-      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>186</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
@@ -4157,150 +4076,43 @@
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" t="s">
-        <v>197</v>
-      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D9" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" t="s">
-        <v>191</v>
-      </c>
-      <c r="D10" t="s">
-        <v>199</v>
-      </c>
-    </row>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" t="s">
-        <v>200</v>
-      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D13" t="s">
-        <v>202</v>
-      </c>
-    </row>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>209</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>210</v>
-      </c>
+      <c r="B14" s="2"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>246</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D16" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>248</v>
-      </c>
-      <c r="B17" t="s">
-        <v>254</v>
-      </c>
-      <c r="D17" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>250</v>
-      </c>
-      <c r="B18" t="s">
-        <v>256</v>
-      </c>
-      <c r="D18" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>266</v>
-      </c>
-      <c r="B19" t="s">
-        <v>268</v>
-      </c>
-      <c r="D19" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>269</v>
-      </c>
-      <c r="B21" t="s">
-        <v>269</v>
-      </c>
-      <c r="D21" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5277,12 +5089,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5007CE1-A05D-4745-B7EA-4E0BD0A3B111}">
-  <dimension ref="A1:C25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B409EA-78AE-4EDC-AD3C-5E59FD94E42A}">
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="72.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="182.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="115" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5299,182 +5111,181 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>231</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>234</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="B6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>236</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>137</v>
+        <v>239</v>
       </c>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>141</v>
+        <v>241</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>143</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C15" t="s">
-        <v>144</v>
-      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>242</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>147</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" t="s">
-        <v>148</v>
-      </c>
+      <c r="B17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B21">
-        <v>85</v>
+        <v>244</v>
+      </c>
+      <c r="B21" s="6">
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B22">
-        <v>50</v>
+        <v>245</v>
+      </c>
+      <c r="B22" s="6">
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B23">
-        <v>85</v>
+        <v>246</v>
+      </c>
+      <c r="B23" s="6">
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B24">
-        <v>85</v>
+        <v>247</v>
+      </c>
+      <c r="B24" s="6">
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>153</v>
-      </c>
-      <c r="B25">
+        <v>248</v>
+      </c>
+      <c r="B25" s="6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B26" s="6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="6">
         <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5502,118 +5313,118 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="B13" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="C15" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="B18">
         <v>50</v>
@@ -5621,7 +5432,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="B19">
         <v>85</v>
@@ -5629,7 +5440,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="B20">
         <v>50</v>
@@ -5715,44 +5526,44 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
       <c r="B3" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="C3" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="B6" t="b">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="C7" t="s">
-        <v>267</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A488A9B2-4542-4D63-B100-D8011444304D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781C77F1-16EB-4ADC-8A9E-F1B0299AD955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="247">
   <si>
     <t>Name</t>
   </si>
@@ -449,15 +449,9 @@
     <t>List of fields which will be checked versus a specific confidence threshold. All new entries must have the "-Confidence" suffix</t>
   </si>
   <si>
-    <t>OtherConfidenceFields</t>
-  </si>
-  <si>
     <t>List of fields which will be checked versus a single confidence #:  Other-Confidence</t>
   </si>
   <si>
-    <t>other-Confidence</t>
-  </si>
-  <si>
     <t>AlwaysValidateClassification</t>
   </si>
   <si>
@@ -728,64 +722,61 @@
     <t>SettlementStatements</t>
   </si>
   <si>
+    <t>LogMessage_SettlementPostProcessing</t>
+  </si>
+  <si>
+    <t>Starting Settlement Post Processing</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_DateFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_MandatoryFieldsFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_LineAmountFailureMath</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_LineAmountFailureEmpty</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_AlreadySetFalse</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_SubtotalFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_TotalFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_SubtotalPass</t>
+  </si>
+  <si>
+    <t>LogMessage_SettlementPostProcessing_ConfidenceFieldsFailure</t>
+  </si>
+  <si>
+    <t>Meter Number,Meter Name,Production Date,Pressure Base,MCF,MMBTU</t>
+  </si>
+  <si>
+    <t>Meter Number-Confidence</t>
+  </si>
+  <si>
+    <t>Meter Name-Confidence</t>
+  </si>
+  <si>
+    <t>Production Date-Confidence</t>
+  </si>
+  <si>
+    <t>Pressure Base-Confidence</t>
+  </si>
+  <si>
+    <t>MCF-Confidence</t>
+  </si>
+  <si>
+    <t>MMBTU-Confidence</t>
+  </si>
+  <si>
     <t>True</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing</t>
-  </si>
-  <si>
-    <t>Starting Settlement Post Processing</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_DateFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_MandatoryFieldsFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_LineAmountFailureMath</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_LineAmountFailureEmpty</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_AlreadySetFalse</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_SubtotalFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_TotalFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_SubtotalPass</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_ConfidenceFieldsFailure</t>
-  </si>
-  <si>
-    <t>Meter Number,Meter Name,Production Date,Pressure Base,MCF,MMBTU</t>
-  </si>
-  <si>
-    <t>BTU,Basis,Allocation Decimal,Gas Lift MCF,Gas Lift MMBTU1,Diverted Gas MCF,Diverted Gas MMBTU</t>
-  </si>
-  <si>
-    <t>Meter Number-Confidence</t>
-  </si>
-  <si>
-    <t>Meter Name-Confidence</t>
-  </si>
-  <si>
-    <t>Production Date-Confidence</t>
-  </si>
-  <si>
-    <t>Pressure Base-Confidence</t>
-  </si>
-  <si>
-    <t>MCF-Confidence</t>
-  </si>
-  <si>
-    <t>MMBTU-Confidence</t>
   </si>
 </sst>
 </file>
@@ -857,7 +848,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -868,7 +859,6 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1263,7 +1253,7 @@
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1358,58 +1348,58 @@
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B14" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" t="s">
         <v>202</v>
-      </c>
-      <c r="C14" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1419,13 +1409,13 @@
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B21">
         <v>0.5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1433,13 +1423,13 @@
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1447,13 +1437,13 @@
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>219</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="C25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1464,10 +1454,10 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1475,10 +1465,10 @@
         <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C28" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1486,10 +1476,10 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1497,10 +1487,10 @@
         <v>113</v>
       </c>
       <c r="B30" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1508,10 +1498,10 @@
         <v>77</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C31" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1519,10 +1509,10 @@
         <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C32" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2597,13 +2587,13 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B7">
         <v>99999</v>
       </c>
       <c r="C7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2630,7 +2620,7 @@
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2702,7 +2692,7 @@
         <v>75</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2718,7 +2708,7 @@
         <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2726,7 +2716,7 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2742,7 +2732,7 @@
         <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2782,7 +2772,7 @@
         <v>76</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2798,7 +2788,7 @@
         <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2814,7 +2804,7 @@
         <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2827,18 +2817,18 @@
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B36" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2859,18 +2849,18 @@
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2926,18 +2916,18 @@
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B51" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B52" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2966,10 +2956,10 @@
     </row>
     <row r="56" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B56" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2986,7 +2976,7 @@
         <v>100</v>
       </c>
       <c r="B59" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2995,7 +2985,7 @@
         <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3020,7 +3010,7 @@
         <v>31</v>
       </c>
       <c r="B65" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4043,10 +4033,10 @@
         <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
         <v>38</v>
@@ -5090,7 +5080,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B409EA-78AE-4EDC-AD3C-5E59FD94E42A}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.5703125" bestFit="1" customWidth="1"/>
@@ -5111,15 +5101,15 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B4" t="s">
         <v>122</v>
@@ -5127,7 +5117,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B5" t="s">
         <v>123</v>
@@ -5135,7 +5125,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B6" t="s">
         <v>124</v>
@@ -5143,7 +5133,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B7" t="s">
         <v>125</v>
@@ -5151,7 +5141,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
         <v>126</v>
@@ -5159,7 +5149,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B9" t="s">
         <v>127</v>
@@ -5167,7 +5157,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B10" t="s">
         <v>128</v>
@@ -5175,7 +5165,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B11" t="s">
         <v>129</v>
@@ -5183,7 +5173,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B13" t="s">
         <v>130</v>
@@ -5197,7 +5187,7 @@
         <v>132</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C16" t="s">
         <v>133</v>
@@ -5211,77 +5201,61 @@
         <v>135</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C18" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C19" t="s">
-        <v>138</v>
-      </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B21" s="6">
+        <v>240</v>
+      </c>
+      <c r="B21">
         <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B22" s="6">
+        <v>241</v>
+      </c>
+      <c r="B22">
         <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B23" s="6">
+        <v>242</v>
+      </c>
+      <c r="B23">
         <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B24" s="6">
+        <v>243</v>
+      </c>
+      <c r="B24">
         <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>248</v>
-      </c>
-      <c r="B25" s="6">
+        <v>244</v>
+      </c>
+      <c r="B25">
         <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>249</v>
-      </c>
-      <c r="B26" s="6">
+        <v>245</v>
+      </c>
+      <c r="B26">
         <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>139</v>
-      </c>
-      <c r="B27" s="6">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -5313,15 +5287,15 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
         <v>122</v>
@@ -5329,7 +5303,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
         <v>123</v>
@@ -5337,7 +5311,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
         <v>126</v>
@@ -5345,7 +5319,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
         <v>128</v>
@@ -5353,15 +5327,15 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B10" t="s">
         <v>130</v>
@@ -5369,10 +5343,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C12" t="s">
         <v>131</v>
@@ -5380,10 +5354,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C13" t="s">
         <v>133</v>
@@ -5391,10 +5365,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C14" t="s">
         <v>134</v>
@@ -5402,10 +5376,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C15" t="s">
         <v>136</v>
@@ -5413,18 +5387,18 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B18">
         <v>50</v>
@@ -5432,7 +5406,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B19">
         <v>85</v>
@@ -5440,7 +5414,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B20">
         <v>50</v>
@@ -5526,44 +5500,44 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B6" t="b">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781C77F1-16EB-4ADC-8A9E-F1B0299AD955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2968AC49-8B5F-46C0-9751-5DD61E375299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="246">
   <si>
     <t>Name</t>
   </si>
@@ -774,9 +774,6 @@
   </si>
   <si>
     <t>MMBTU-Confidence</t>
-  </si>
-  <si>
-    <t>True</t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1360,7 @@
         <v>138</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>154</v>
@@ -1412,7 +1409,7 @@
         <v>168</v>
       </c>
       <c r="B21">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>169</v>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2968AC49-8B5F-46C0-9751-5DD61E375299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715FDAE3-72F4-4326-95F5-A69E24D27488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="252">
   <si>
     <t>Name</t>
   </si>
@@ -774,6 +774,24 @@
   </si>
   <si>
     <t>MMBTU-Confidence</t>
+  </si>
+  <si>
+    <t>Initsheet</t>
+  </si>
+  <si>
+    <t>01 Hiland-Hiland-Bakken</t>
+  </si>
+  <si>
+    <t>Data\Exports\Output.xlsx</t>
+  </si>
+  <si>
+    <t>OutputFile</t>
+  </si>
+  <si>
+    <t>ReportPath</t>
+  </si>
+  <si>
+    <t>Data\Exports\Report.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1512,21 +1530,42 @@
         <v>167</v>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>246</v>
+      </c>
+      <c r="B34" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>249</v>
+      </c>
+      <c r="B35" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>250</v>
+      </c>
+      <c r="B36" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715FDAE3-72F4-4326-95F5-A69E24D27488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D14625-94E1-43F2-9BB9-00DB539A2C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="268">
   <si>
     <t>Name</t>
   </si>
@@ -792,6 +792,56 @@
   </si>
   <si>
     <t>Data\Exports\Report.xlsx</t>
+  </si>
+  <si>
+    <t>ReportSheet</t>
+  </si>
+  <si>
+    <t>Report</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>chaitanya.ravindra@accelirate.com</t>
+  </si>
+  <si>
+    <t>ConocoPhillips Process Start</t>
+  </si>
+  <si>
+    <t>StartBody</t>
+  </si>
+  <si>
+    <t>StartSubject</t>
+  </si>
+  <si>
+    <t>EndSubject</t>
+  </si>
+  <si>
+    <t>EndBody</t>
+  </si>
+  <si>
+    <t>ConocoPhillips Process End</t>
+  </si>
+  <si>
+    <t>Hello,
+Conocophillips process has ended at {StartTime}.
+Regards</t>
+  </si>
+  <si>
+    <t>Hello,&lt;br&gt;&lt;br&gt;The &lt;b&gt;Conocophillips&lt;/b&gt; process has started.&lt;br&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Start Time:&lt;/b&gt; {StartTime}&lt;/li&gt;&lt;li&gt;&lt;b&gt;Machine:&lt;/b&gt; {MachineName}&lt;/li&gt;&lt;li&gt;&lt;b&gt;Source Queue:&lt;/b&gt; {QueueName}&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;Regards,&lt;br&gt;Accelirate</t>
+  </si>
+  <si>
+    <t>OrchestratorQueueName</t>
+  </si>
+  <si>
+    <t>SettlementStatement</t>
+  </si>
+  <si>
+    <t>Delay</t>
+  </si>
+  <si>
+    <t>00h 00m 05.000s</t>
   </si>
 </sst>
 </file>
@@ -863,7 +913,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -873,6 +923,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1233,8 +1286,12 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+      <c r="A2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>265</v>
+      </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -1554,15 +1611,64 @@
         <v>251</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>252</v>
+      </c>
+      <c r="B37" t="s">
+        <v>253</v>
+      </c>
+    </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>254</v>
+      </c>
+      <c r="B39" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B40" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>266</v>
+      </c>
+      <c r="B45" t="s">
+        <v>267</v>
+      </c>
+    </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D14625-94E1-43F2-9BB9-00DB539A2C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92676D51-013F-47DF-B79A-22E5DED73F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="266">
   <si>
     <t>Name</t>
   </si>
@@ -722,39 +722,9 @@
     <t>SettlementStatements</t>
   </si>
   <si>
-    <t>LogMessage_SettlementPostProcessing</t>
-  </si>
-  <si>
     <t>Starting Settlement Post Processing</t>
   </si>
   <si>
-    <t>LogMessage_SettlementPostProcessing_DateFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_MandatoryFieldsFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_LineAmountFailureMath</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_LineAmountFailureEmpty</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_AlreadySetFalse</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_SubtotalFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_TotalFailure</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_SubtotalPass</t>
-  </si>
-  <si>
-    <t>LogMessage_SettlementPostProcessing_ConfidenceFieldsFailure</t>
-  </si>
-  <si>
     <t>Meter Number,Meter Name,Production Date,Pressure Base,MCF,MMBTU</t>
   </si>
   <si>
@@ -824,24 +794,48 @@
     <t>ConocoPhillips Process End</t>
   </si>
   <si>
+    <t>Hello,&lt;br&gt;&lt;br&gt;The &lt;b&gt;Conocophillips&lt;/b&gt; process has started.&lt;br&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Start Time:&lt;/b&gt; {StartTime}&lt;/li&gt;&lt;li&gt;&lt;b&gt;Machine:&lt;/b&gt; {MachineName}&lt;/li&gt;&lt;li&gt;&lt;b&gt;Source Queue:&lt;/b&gt; {QueueName}&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;Regards,&lt;br&gt;Accelirate</t>
+  </si>
+  <si>
+    <t>OrchestratorQueueName</t>
+  </si>
+  <si>
+    <t>SettlementStatement</t>
+  </si>
+  <si>
+    <t>LogMessage_InvoicePostProcessing</t>
+  </si>
+  <si>
+    <t>LogMessage_InvoicePostProcessing_DateFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_InvoicePostProcessing_MandatoryFieldsFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_InvoicePostProcessing_LineAmountFailureMath</t>
+  </si>
+  <si>
+    <t>LogMessage_InvoicePostProcessing_LineAmountFailureEmpty</t>
+  </si>
+  <si>
+    <t>LogMessage_InvoicePostProcessing_AlreadySetFalse</t>
+  </si>
+  <si>
+    <t>LogMessage_InvoicePostProcessing_SubtotalFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_InvoicePostProcessing_TotalFailure</t>
+  </si>
+  <si>
+    <t>LogMessage_InvoicePostProcessing_SubtotalPass</t>
+  </si>
+  <si>
+    <t>LogMessage_InvoicePostProcessing_ConfidenceFieldsFailure</t>
+  </si>
+  <si>
     <t>Hello,
-Conocophillips process has ended at {StartTime}.
+Conocophillips process has ended at {EndTime}.
 Regards</t>
-  </si>
-  <si>
-    <t>Hello,&lt;br&gt;&lt;br&gt;The &lt;b&gt;Conocophillips&lt;/b&gt; process has started.&lt;br&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Start Time:&lt;/b&gt; {StartTime}&lt;/li&gt;&lt;li&gt;&lt;b&gt;Machine:&lt;/b&gt; {MachineName}&lt;/li&gt;&lt;li&gt;&lt;b&gt;Source Queue:&lt;/b&gt; {QueueName}&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;Regards,&lt;br&gt;Accelirate</t>
-  </si>
-  <si>
-    <t>OrchestratorQueueName</t>
-  </si>
-  <si>
-    <t>SettlementStatement</t>
-  </si>
-  <si>
-    <t>Delay</t>
-  </si>
-  <si>
-    <t>00h 00m 05.000s</t>
   </si>
 </sst>
 </file>
@@ -1287,10 +1281,10 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1589,86 +1583,79 @@
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B34" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B35" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B36" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B37" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B39" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B40" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>266</v>
-      </c>
-      <c r="B45" t="s">
-        <v>267</v>
-      </c>
-    </row>
+    <row r="45" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2754,7 +2741,7 @@
         <v>48</v>
       </c>
       <c r="B9">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>114</v>
@@ -5225,7 +5212,7 @@
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="66.85546875" customWidth="1"/>
     <col min="2" max="2" width="182.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="115" bestFit="1" customWidth="1"/>
   </cols>
@@ -5243,15 +5230,15 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" t="s">
         <v>228</v>
-      </c>
-      <c r="B3" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="B4" t="s">
         <v>122</v>
@@ -5259,7 +5246,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="B5" t="s">
         <v>123</v>
@@ -5267,7 +5254,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="B6" t="s">
         <v>124</v>
@@ -5275,7 +5262,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="B7" t="s">
         <v>125</v>
@@ -5283,7 +5270,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="B8" t="s">
         <v>126</v>
@@ -5291,7 +5278,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="B9" t="s">
         <v>127</v>
@@ -5299,7 +5286,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="B10" t="s">
         <v>128</v>
@@ -5307,7 +5294,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="B11" t="s">
         <v>129</v>
@@ -5315,7 +5302,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="B13" t="s">
         <v>130</v>
@@ -5329,7 +5316,7 @@
         <v>132</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C16" t="s">
         <v>133</v>
@@ -5343,7 +5330,7 @@
         <v>135</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C18" t="s">
         <v>136</v>
@@ -5354,7 +5341,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B21">
         <v>80</v>
@@ -5362,7 +5349,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B22">
         <v>80</v>
@@ -5370,7 +5357,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="B23">
         <v>80</v>
@@ -5378,7 +5365,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B24">
         <v>80</v>
@@ -5386,7 +5373,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B25">
         <v>80</v>
@@ -5394,7 +5381,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B26">
         <v>80</v>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92676D51-013F-47DF-B79A-22E5DED73F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54F0A88-1576-4FBB-A88F-BB9739864155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="268">
   <si>
     <t>Name</t>
   </si>
@@ -251,9 +251,6 @@
     <t>Presenting Validation Station for:</t>
   </si>
   <si>
-    <t>Data\Exports\</t>
-  </si>
-  <si>
     <t>Data\ReceiptsTraining\</t>
   </si>
   <si>
@@ -746,24 +743,12 @@
     <t>MMBTU-Confidence</t>
   </si>
   <si>
-    <t>Initsheet</t>
-  </si>
-  <si>
-    <t>01 Hiland-Hiland-Bakken</t>
-  </si>
-  <si>
-    <t>Data\Exports\Output.xlsx</t>
-  </si>
-  <si>
     <t>OutputFile</t>
   </si>
   <si>
     <t>ReportPath</t>
   </si>
   <si>
-    <t>Data\Exports\Report.xlsx</t>
-  </si>
-  <si>
     <t>ReportSheet</t>
   </si>
   <si>
@@ -792,9 +777,6 @@
   </si>
   <si>
     <t>ConocoPhillips Process End</t>
-  </si>
-  <si>
-    <t>Hello,&lt;br&gt;&lt;br&gt;The &lt;b&gt;Conocophillips&lt;/b&gt; process has started.&lt;br&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Start Time:&lt;/b&gt; {StartTime}&lt;/li&gt;&lt;li&gt;&lt;b&gt;Machine:&lt;/b&gt; {MachineName}&lt;/li&gt;&lt;li&gt;&lt;b&gt;Source Queue:&lt;/b&gt; {QueueName}&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;Regards,&lt;br&gt;Accelirate</t>
   </si>
   <si>
     <t>OrchestratorQueueName</t>
@@ -836,6 +818,30 @@
     <t>Hello,
 Conocophillips process has ended at {EndTime}.
 Regards</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\Exports\Output.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\Exports\Report.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\Exports\</t>
+  </si>
+  <si>
+    <t>MaxRetry</t>
+  </si>
+  <si>
+    <t>ProcessName</t>
+  </si>
+  <si>
+    <t>EXCEL</t>
+  </si>
+  <si>
+    <t>Hello,&lt;br&gt;&lt;br&gt;The &lt;b&gt;Conocophillips&lt;/b&gt; process has started.&lt;br&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Start Time:&lt;/b&gt; {StartTime}&lt;/li&gt;&lt;li&gt;&lt;b&gt;Source Queue:&lt;/b&gt; {QueueName}&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;Regards,&lt;br&gt;Accelirate</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1246,7 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.85546875" customWidth="1"/>
-    <col min="2" max="2" width="70.140625" customWidth="1"/>
+    <col min="2" max="2" width="88.85546875" customWidth="1"/>
     <col min="3" max="3" width="131.7109375" customWidth="1"/>
     <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
@@ -1281,10 +1287,10 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1313,13 +1319,13 @@
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1327,7 +1333,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>263</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -1338,7 +1344,7 @@
         <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
@@ -1349,7 +1355,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
         <v>65</v>
@@ -1387,7 +1393,7 @@
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1395,77 +1401,77 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
         <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" t="s">
         <v>201</v>
-      </c>
-      <c r="B14" t="s">
-        <v>200</v>
-      </c>
-      <c r="C14" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>153</v>
+        <v>260</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>153</v>
+        <v>260</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1475,13 +1481,13 @@
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21">
+        <v>0.7</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="B21">
-        <v>0.6</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1489,13 +1495,13 @@
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C23" t="s">
         <v>196</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C23" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1503,13 +1509,13 @@
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>218</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" t="s">
         <v>219</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C25" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1520,10 +1526,10 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1531,10 +1537,10 @@
         <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1542,120 +1548,120 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C32" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>236</v>
-      </c>
-      <c r="B34" t="s">
-        <v>237</v>
-      </c>
-    </row>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B35" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B36" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B37" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B39" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B40" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B43" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B45" t="s">
+        <v>266</v>
+      </c>
+    </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2678,62 +2684,62 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B7">
         <v>99999</v>
       </c>
       <c r="C7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B8">
         <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2741,24 +2747,31 @@
         <v>48</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>264</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
@@ -2802,10 +2815,10 @@
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2818,10 +2831,10 @@
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2837,7 +2850,7 @@
         <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2845,7 +2858,7 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2861,7 +2874,7 @@
         <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2874,10 +2887,10 @@
     </row>
     <row r="27" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
         <v>90</v>
-      </c>
-      <c r="B27" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2898,10 +2911,10 @@
     </row>
     <row r="30" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2917,7 +2930,7 @@
         <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2933,7 +2946,7 @@
         <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2946,18 +2959,18 @@
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>208</v>
+      </c>
+      <c r="B36" t="s">
         <v>209</v>
-      </c>
-      <c r="B36" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>210</v>
+      </c>
+      <c r="B37" t="s">
         <v>211</v>
-      </c>
-      <c r="B37" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2978,134 +2991,134 @@
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" t="s">
         <v>118</v>
-      </c>
-      <c r="B44" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" t="s">
         <v>93</v>
-      </c>
-      <c r="B46" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" t="s">
         <v>111</v>
-      </c>
-      <c r="B50" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>191</v>
+      </c>
+      <c r="B51" t="s">
         <v>192</v>
-      </c>
-      <c r="B51" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" t="s">
         <v>194</v>
-      </c>
-      <c r="B52" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" t="s">
         <v>101</v>
-      </c>
-      <c r="B53" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" t="s">
         <v>105</v>
-      </c>
-      <c r="B54" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>197</v>
+      </c>
+      <c r="B56" t="s">
         <v>198</v>
-      </c>
-      <c r="B56" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>97</v>
+      </c>
+      <c r="B58" t="s">
         <v>98</v>
-      </c>
-      <c r="B58" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3114,7 +3127,7 @@
         <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3139,7 +3152,7 @@
         <v>31</v>
       </c>
       <c r="B65" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4162,10 +4175,10 @@
         <v>40</v>
       </c>
       <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
         <v>223</v>
-      </c>
-      <c r="C2" t="s">
-        <v>224</v>
       </c>
       <c r="D2" t="s">
         <v>38</v>
@@ -5230,82 +5243,82 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -5313,13 +5326,13 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C16" t="s">
         <v>132</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C16" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -5327,13 +5340,13 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" t="s">
         <v>135</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C18" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -5341,7 +5354,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B21">
         <v>80</v>
@@ -5349,7 +5362,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B22">
         <v>80</v>
@@ -5357,7 +5370,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B23">
         <v>80</v>
@@ -5365,7 +5378,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B24">
         <v>80</v>
@@ -5373,7 +5386,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B25">
         <v>80</v>
@@ -5381,7 +5394,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B26">
         <v>80</v>
@@ -5416,118 +5429,118 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" t="s">
         <v>170</v>
-      </c>
-      <c r="B3" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" t="s">
         <v>176</v>
-      </c>
-      <c r="B8" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
         <v>179</v>
       </c>
-      <c r="B12" t="s">
-        <v>180</v>
-      </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" t="s">
         <v>181</v>
       </c>
-      <c r="B13" t="s">
-        <v>182</v>
-      </c>
       <c r="C13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" t="s">
         <v>183</v>
       </c>
-      <c r="B14" t="s">
-        <v>184</v>
-      </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B15" t="s">
         <v>185</v>
       </c>
-      <c r="B15" t="s">
-        <v>186</v>
-      </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" t="s">
         <v>187</v>
       </c>
-      <c r="B16" t="s">
-        <v>188</v>
-      </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18">
         <v>50</v>
@@ -5535,7 +5548,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B19">
         <v>85</v>
@@ -5543,7 +5556,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B20">
         <v>50</v>
@@ -5629,44 +5642,44 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" t="s">
         <v>203</v>
-      </c>
-      <c r="B3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C3" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B6" t="b">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" t="s">
         <v>217</v>
-      </c>
-      <c r="C7" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
